--- a/태화라이온스 회원명부.xlsx
+++ b/태화라이온스 회원명부.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\내 드라이브\이재원\클로드코딩\태화라이온스\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FEC7DE48-BE67-4E54-AE79-5C41B1A3AD5A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4EB24F39-AA5A-4B39-B3A0-B2B7BC4D727F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-51720" yWindow="-5475" windowWidth="51840" windowHeight="21120" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="115">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="115">
   <si>
     <t>장태원</t>
   </si>
@@ -979,7 +979,9 @@
       <c r="C3" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="D3" s="3"/>
+      <c r="D3" s="1" t="s">
+        <v>112</v>
+      </c>
     </row>
     <row r="4" spans="1:4" ht="48.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
@@ -1225,7 +1227,9 @@
       <c r="C23" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="D23" s="3"/>
+      <c r="D23" s="1" t="s">
+        <v>112</v>
+      </c>
     </row>
     <row r="24" spans="1:4" ht="48.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="1" t="s">
@@ -1273,7 +1277,9 @@
       <c r="C27" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="D27" s="3"/>
+      <c r="D27" s="1" t="s">
+        <v>112</v>
+      </c>
     </row>
     <row r="28" spans="1:4" ht="48.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="1" t="s">
